--- a/docs/oc-mensuales/licencia-de-software-de-ofimatica/ene-2026.xlsx
+++ b/docs/oc-mensuales/licencia-de-software-de-ofimatica/ene-2026.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M37"/>
+  <dimension ref="A1:M36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -2041,7 +2041,7 @@
         </is>
       </c>
       <c r="M26" s="2" t="n">
-        <v>12754.5747</v>
+        <v>12754.57</v>
       </c>
     </row>
     <row r="27">
@@ -2108,7 +2108,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>598-13-SE26</t>
+          <t>3447-162-CM26</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2128,32 +2128,32 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Enviada a Proveedor</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>61.513.000-1</t>
+          <t>69.265.100-6</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>DIRECCION PREVISION DE CARABINEROS DE CHILE</t>
+          <t>MUNICIPALIDAD DE ALTO HOSPICIO</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>Tarapacá</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>SEIDOR TECHNOLOGIES S.A.</t>
+          <t>CLOUDLATAM SPA</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>76.449.580-2</t>
+          <t>76.981.642-9</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
@@ -2163,17 +2163,17 @@
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M28" s="2" t="n">
-        <v>330128295.84</v>
+        <v>84469.77</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>3447-162-CM26</t>
+          <t>4455-16-CM26</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2188,7 +2188,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2026-01-23</t>
+          <t>2026-01-26</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -2198,47 +2198,43 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>69.265.100-6</t>
+          <t>69.160.100-5</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>MUNICIPALIDAD DE ALTO HOSPICIO</t>
+          <t>I MUNICIPALIDAD DE ARAUCO</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Tarapacá</t>
+          <t>Bío-Bío</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>CLOUDLATAM SPA</t>
+          <t>COMPUTACION INTEGRAL S A</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>76.981.642-9</t>
-        </is>
-      </c>
-      <c r="K29" t="inlineStr">
-        <is>
-          <t>Región Metropolitana de Santiago</t>
-        </is>
-      </c>
+          <t>96.689.970-0</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr"/>
       <c r="L29" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M29" s="2" t="n">
-        <v>84469.77</v>
+        <v>2113.8</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>4455-16-CM26</t>
+          <t>4609-42-CM26</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2253,7 +2249,7 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2026-01-26</t>
+          <t>2026-01-27</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -2263,27 +2259,27 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>69.160.100-5</t>
+          <t>69.240.400-9</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE ARAUCO</t>
+          <t>I MUNICIPALIDAD DE CHILE CHICO</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Aysén</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>COMPUTACION INTEGRAL S A</t>
+          <t>SUPER SOFTWARE SPA</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>96.689.970-0</t>
+          <t>76.486.150-7</t>
         </is>
       </c>
       <c r="K30" t="inlineStr"/>
@@ -2293,13 +2289,13 @@
         </is>
       </c>
       <c r="M30" s="2" t="n">
-        <v>2113.8</v>
+        <v>22463.39</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>4609-42-CM26</t>
+          <t>1561-14-CM26</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2324,27 +2320,27 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>69.240.400-9</t>
+          <t>61.504.000-2</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CHILE CHICO</t>
+          <t>DIRECCION GENERAL DEL CREDITO PRENDARIO</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Aysén</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>SUPER SOFTWARE SPA</t>
+          <t>TECNOLOGIA BS SPA</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>76.486.150-7</t>
+          <t>76.852.815-2</t>
         </is>
       </c>
       <c r="K31" t="inlineStr"/>
@@ -2354,13 +2350,13 @@
         </is>
       </c>
       <c r="M31" s="2" t="n">
-        <v>22463.39</v>
+        <v>4615.65</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>1561-14-CM26</t>
+          <t>483-50-CM26</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2375,7 +2371,7 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2026-01-27</t>
+          <t>2026-01-28</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -2385,27 +2381,27 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>61.504.000-2</t>
+          <t>61.607.103-3</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>DIRECCION GENERAL DEL CREDITO PRENDARIO</t>
+          <t>SERVICIO DE SALUD CONCEPCION ARAUCO HOSPITAL DE CONTULMO</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Bío-Bío</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>TECNOLOGIA BS SPA</t>
+          <t>OPTIMIZA SEGURIDAD SPA</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>76.852.815-2</t>
+          <t>76.854.651-7</t>
         </is>
       </c>
       <c r="K32" t="inlineStr"/>
@@ -2415,13 +2411,13 @@
         </is>
       </c>
       <c r="M32" s="2" t="n">
-        <v>4615.65</v>
+        <v>5097.96</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>483-50-CM26</t>
+          <t>2412-50-CM26</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2446,27 +2442,27 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>61.607.103-3</t>
+          <t>69.254.100-6</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD CONCEPCION ARAUCO HOSPITAL DE CONTULMO</t>
+          <t>I MUNICIPALIDAD DE LO PRADO</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>OPTIMIZA SEGURIDAD SPA</t>
+          <t>COMPUTACION INTEGRAL S A</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>76.854.651-7</t>
+          <t>96.689.970-0</t>
         </is>
       </c>
       <c r="K33" t="inlineStr"/>
@@ -2476,13 +2472,13 @@
         </is>
       </c>
       <c r="M33" s="2" t="n">
-        <v>5097.96</v>
+        <v>5284.49</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2412-50-CM26</t>
+          <t>2577-6-CM26</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2507,12 +2503,12 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>69.254.100-6</t>
+          <t>69.070.100-6</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LO PRADO</t>
+          <t>I MUNICIPALIDAD DE SANTIAGO</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -2522,12 +2518,12 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>COMPUTACION INTEGRAL S A</t>
+          <t>COMERCIALIZADORA TELENET LTDA</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>96.689.970-0</t>
+          <t>77.700.780-7</t>
         </is>
       </c>
       <c r="K34" t="inlineStr"/>
@@ -2537,13 +2533,13 @@
         </is>
       </c>
       <c r="M34" s="2" t="n">
-        <v>5284.49</v>
+        <v>10780.36</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2577-6-CM26</t>
+          <t>730736-23-CM26</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2558,7 +2554,7 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2026-01-28</t>
+          <t>2026-01-30</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -2568,27 +2564,27 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>69.070.100-6</t>
+          <t>69.090.900-6</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE SANTIAGO</t>
+          <t>I MUNICIPALIDAD DE PAREDONES</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Lib. Gral. Bdo. O'Higgins</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA TELENET LTDA</t>
+          <t>TECNOLOGIA BS SPA</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>77.700.780-7</t>
+          <t>76.852.815-2</t>
         </is>
       </c>
       <c r="K35" t="inlineStr"/>
@@ -2598,13 +2594,13 @@
         </is>
       </c>
       <c r="M35" s="2" t="n">
-        <v>10780.36</v>
+        <v>13846.96</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>730736-23-CM26</t>
+          <t>3866-3-CM26</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2629,17 +2625,17 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>69.090.900-6</t>
+          <t>69.251.300-2</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PAREDONES</t>
+          <t>I MUNICIPALIDAD DE PRIMAVERA</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>Magallanes y Antártica</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
@@ -2659,67 +2655,6 @@
         </is>
       </c>
       <c r="M36" s="2" t="n">
-        <v>13846.96</v>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>3866-3-CM26</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>2239-11-LR24</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>ene-2026</t>
-        </is>
-      </c>
-      <c r="D37" t="inlineStr">
-        <is>
-          <t>2026-01-30</t>
-        </is>
-      </c>
-      <c r="E37" t="inlineStr">
-        <is>
-          <t>Recepcion Conforme</t>
-        </is>
-      </c>
-      <c r="F37" t="inlineStr">
-        <is>
-          <t>69.251.300-2</t>
-        </is>
-      </c>
-      <c r="G37" t="inlineStr">
-        <is>
-          <t>I MUNICIPALIDAD DE PRIMAVERA</t>
-        </is>
-      </c>
-      <c r="H37" t="inlineStr">
-        <is>
-          <t>Magallanes y Antártica</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>TECNOLOGIA BS SPA</t>
-        </is>
-      </c>
-      <c r="J37" t="inlineStr">
-        <is>
-          <t>76.852.815-2</t>
-        </is>
-      </c>
-      <c r="K37" t="inlineStr"/>
-      <c r="L37" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="M37" s="2" t="n">
         <v>9231.309999999999</v>
       </c>
     </row>
